--- a/population-projection/src/main/resources/population_data/USSR/USSR-population-ADH.xlsx
+++ b/population-projection/src/main/resources/population_data/USSR/USSR-population-ADH.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\population-time-progression\src\main\resources\population_data\USSR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\population-projection\src\main\resources\population_data\USSR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B01CB27-9CCD-4107-A216-30BAA3365106}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16BCCA6-BB9B-49E8-BEA7-B4AC7190A7DE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5670" yWindow="2940" windowWidth="28410" windowHeight="19065" activeTab="1" xr2:uid="{B2C1D4B7-982B-4E43-A286-03A182DA63D3}"/>
+    <workbookView xWindow="5430" yWindow="1590" windowWidth="23985" windowHeight="21000" activeTab="2" xr2:uid="{B2C1D4B7-982B-4E43-A286-03A182DA63D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Comment" sheetId="3" r:id="rId1"/>
@@ -510,15 +510,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F905400-5B75-4692-AB87-C288B685BE8C}">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="11.28515625" customWidth="1"/>
-    <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="19.42578125" customWidth="1"/>
+    <col min="1" max="8" width="11.28515625" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -529,31 +529,40 @@
         <v>1927</v>
       </c>
       <c r="D1" s="7">
+        <v>1934</v>
+      </c>
+      <c r="E1" s="7">
+        <v>1935</v>
+      </c>
+      <c r="F1" s="7">
+        <v>1936</v>
+      </c>
+      <c r="G1" s="7">
         <v>1937</v>
       </c>
-      <c r="E1" s="7">
+      <c r="H1" s="7">
         <v>1938</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="7">
+      <c r="K1" s="7">
         <v>1940</v>
       </c>
-      <c r="I1" s="7">
+      <c r="L1" s="7">
         <v>1941</v>
       </c>
-      <c r="J1" s="7">
+      <c r="M1" s="7">
         <v>1946</v>
       </c>
-      <c r="K1" s="7">
+      <c r="N1" s="7">
         <v>1947</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
@@ -563,32 +572,41 @@
       <c r="C2" s="4">
         <v>71825</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="4">
+        <v>75253</v>
+      </c>
+      <c r="E2" s="4">
+        <v>75887</v>
+      </c>
+      <c r="F2" s="4">
+        <v>76825</v>
+      </c>
+      <c r="G2" s="5">
         <v>77923</v>
       </c>
-      <c r="E2" s="5">
+      <c r="H2" s="5">
         <v>79265</v>
       </c>
-      <c r="F2" s="4">
+      <c r="I2" s="4">
         <v>80674</v>
       </c>
-      <c r="G2" s="6">
+      <c r="J2" s="6">
         <v>90453</v>
       </c>
-      <c r="H2" s="6">
+      <c r="K2" s="6">
         <v>92316</v>
       </c>
-      <c r="I2" s="6">
+      <c r="L2" s="6">
         <v>93688</v>
       </c>
-      <c r="J2" s="6">
+      <c r="M2" s="6">
         <v>74364</v>
       </c>
-      <c r="K2" s="6">
+      <c r="N2" s="6">
         <v>75234</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -598,32 +616,41 @@
       <c r="C3" s="4">
         <v>12129</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="4">
+        <v>10318</v>
+      </c>
+      <c r="E3" s="4">
+        <v>9717</v>
+      </c>
+      <c r="F3" s="4">
+        <v>9476</v>
+      </c>
+      <c r="G3" s="5">
         <v>9557</v>
       </c>
-      <c r="E3" s="5">
+      <c r="H3" s="5">
         <v>10114</v>
       </c>
-      <c r="F3" s="5">
+      <c r="I3" s="5">
         <v>10752</v>
       </c>
-      <c r="G3" s="6">
+      <c r="J3" s="6">
         <v>11765</v>
       </c>
-      <c r="H3" s="6">
+      <c r="K3" s="6">
         <v>12827</v>
       </c>
-      <c r="I3" s="6">
+      <c r="L3" s="6">
         <v>13242</v>
       </c>
-      <c r="J3" s="6">
+      <c r="M3" s="6">
         <v>6687</v>
       </c>
-      <c r="K3" s="6">
+      <c r="N3" s="6">
         <v>6751</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -633,32 +660,41 @@
       <c r="C4" s="4">
         <v>7544</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
+        <v>10752</v>
+      </c>
+      <c r="E4" s="4">
+        <v>10736</v>
+      </c>
+      <c r="F4" s="4">
+        <v>10537</v>
+      </c>
+      <c r="G4" s="5">
         <v>10179</v>
       </c>
-      <c r="E4" s="5">
+      <c r="H4" s="5">
         <v>9629</v>
       </c>
-      <c r="F4" s="5">
+      <c r="I4" s="5">
         <v>9051</v>
       </c>
-      <c r="G4" s="6">
+      <c r="J4" s="6">
         <v>10043</v>
       </c>
-      <c r="H4" s="6">
+      <c r="K4" s="6">
         <v>9459</v>
       </c>
-      <c r="I4" s="6">
+      <c r="L4" s="6">
         <v>9193</v>
       </c>
-      <c r="J4" s="6">
+      <c r="M4" s="6">
         <v>11006</v>
       </c>
-      <c r="K4" s="6">
+      <c r="N4" s="6">
         <v>10817</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -668,32 +704,41 @@
       <c r="C5" s="4">
         <v>8458</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
+        <v>7845</v>
+      </c>
+      <c r="E5" s="4">
+        <v>8526</v>
+      </c>
+      <c r="F5" s="4">
+        <v>9237</v>
+      </c>
+      <c r="G5" s="5">
         <v>9862</v>
       </c>
-      <c r="E5" s="5">
+      <c r="H5" s="5">
         <v>10284</v>
       </c>
-      <c r="F5" s="5">
+      <c r="I5" s="5">
         <v>10475</v>
       </c>
-      <c r="G5" s="6">
+      <c r="J5" s="6">
         <v>11596</v>
       </c>
-      <c r="H5" s="6">
+      <c r="K5" s="6">
         <v>11551</v>
       </c>
-      <c r="I5" s="6">
+      <c r="L5" s="6">
         <v>11306</v>
       </c>
-      <c r="J5" s="6">
+      <c r="M5" s="6">
         <v>8761</v>
       </c>
-      <c r="K5" s="6">
+      <c r="N5" s="6">
         <v>8795</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
@@ -703,32 +748,41 @@
       <c r="C6" s="4">
         <v>8653</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
+        <v>6944</v>
+      </c>
+      <c r="E6" s="4">
+        <v>6650</v>
+      </c>
+      <c r="F6" s="4">
+        <v>6564</v>
+      </c>
+      <c r="G6" s="5">
         <v>6717</v>
       </c>
-      <c r="E6" s="5">
+      <c r="H6" s="5">
         <v>7096</v>
       </c>
-      <c r="F6" s="5">
+      <c r="I6" s="5">
         <v>7651</v>
       </c>
-      <c r="G6" s="6">
+      <c r="J6" s="6">
         <v>8646</v>
       </c>
-      <c r="H6" s="6">
+      <c r="K6" s="6">
         <v>9390</v>
       </c>
-      <c r="I6" s="6">
+      <c r="L6" s="6">
         <v>10135</v>
       </c>
-      <c r="J6" s="6">
+      <c r="M6" s="6">
         <v>10028</v>
       </c>
-      <c r="K6" s="6">
+      <c r="N6" s="6">
         <v>10016</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
@@ -738,32 +792,41 @@
       <c r="C7" s="4">
         <v>7184</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
+        <v>8259</v>
+      </c>
+      <c r="E7" s="4">
+        <v>8210</v>
+      </c>
+      <c r="F7" s="4">
+        <v>7969</v>
+      </c>
+      <c r="G7" s="5">
         <v>7562</v>
       </c>
-      <c r="E7" s="5">
+      <c r="H7" s="5">
         <v>7115</v>
       </c>
-      <c r="F7" s="5">
+      <c r="I7" s="5">
         <v>6716</v>
       </c>
-      <c r="G7" s="6">
+      <c r="J7" s="6">
         <v>7466</v>
       </c>
-      <c r="H7" s="6">
+      <c r="K7" s="6">
         <v>7181</v>
       </c>
-      <c r="I7" s="6">
+      <c r="L7" s="6">
         <v>7127</v>
       </c>
-      <c r="J7" s="6">
+      <c r="M7" s="6">
         <v>6430</v>
       </c>
-      <c r="K7" s="6">
+      <c r="N7" s="6">
         <v>7191</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
@@ -773,32 +836,41 @@
       <c r="C8" s="4">
         <v>5688</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
+        <v>7041</v>
+      </c>
+      <c r="E8" s="4">
+        <v>7254</v>
+      </c>
+      <c r="F8" s="4">
+        <v>7468</v>
+      </c>
+      <c r="G8" s="5">
         <v>7672</v>
       </c>
-      <c r="E8" s="5">
+      <c r="H8" s="5">
         <v>7858</v>
       </c>
-      <c r="F8" s="5">
+      <c r="I8" s="5">
         <v>7975</v>
       </c>
-      <c r="G8" s="6">
+      <c r="J8" s="6">
         <v>8870</v>
       </c>
-      <c r="H8" s="6">
+      <c r="K8" s="6">
         <v>8818</v>
       </c>
-      <c r="I8" s="6">
+      <c r="L8" s="6">
         <v>8558</v>
       </c>
-      <c r="J8" s="6">
+      <c r="M8" s="6">
         <v>4357</v>
       </c>
-      <c r="K8" s="6">
+      <c r="N8" s="6">
         <v>4455</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>6</v>
       </c>
@@ -808,32 +880,41 @@
       <c r="C9" s="4">
         <v>4403</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="4">
+        <v>5561</v>
+      </c>
+      <c r="E9" s="4">
+        <v>5785</v>
+      </c>
+      <c r="F9" s="4">
+        <v>6028</v>
+      </c>
+      <c r="G9" s="5">
         <v>6287</v>
       </c>
-      <c r="E9" s="5">
+      <c r="H9" s="5">
         <v>6540</v>
       </c>
-      <c r="F9" s="5">
+      <c r="I9" s="5">
         <v>6776</v>
       </c>
-      <c r="G9" s="6">
+      <c r="J9" s="6">
         <v>7592</v>
       </c>
-      <c r="H9" s="6">
+      <c r="K9" s="6">
         <v>7828</v>
       </c>
-      <c r="I9" s="6">
+      <c r="L9" s="6">
         <v>8055</v>
       </c>
-      <c r="J9" s="6">
+      <c r="M9" s="6">
         <v>5156</v>
       </c>
-      <c r="K9" s="6">
+      <c r="N9" s="6">
         <v>4870</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
@@ -843,32 +924,41 @@
       <c r="C10" s="4">
         <v>3739</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
+        <v>4273</v>
+      </c>
+      <c r="E10" s="4">
+        <v>4478</v>
+      </c>
+      <c r="F10" s="4">
+        <v>4693</v>
+      </c>
+      <c r="G10" s="5">
         <v>4899</v>
       </c>
-      <c r="E10" s="5">
+      <c r="H10" s="5">
         <v>5096</v>
       </c>
-      <c r="F10" s="5">
+      <c r="I10" s="5">
         <v>5308</v>
       </c>
-      <c r="G10" s="6">
+      <c r="J10" s="6">
         <v>5959</v>
       </c>
-      <c r="H10" s="6">
+      <c r="K10" s="6">
         <v>6217</v>
       </c>
-      <c r="I10" s="6">
+      <c r="L10" s="6">
         <v>6486</v>
       </c>
-      <c r="J10" s="6">
+      <c r="M10" s="6">
         <v>5006</v>
       </c>
-      <c r="K10" s="6">
+      <c r="N10" s="6">
         <v>5075</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
@@ -878,32 +968,41 @@
       <c r="C11" s="4">
         <v>3200</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="4">
+        <v>3372</v>
+      </c>
+      <c r="E11" s="4">
+        <v>3448</v>
+      </c>
+      <c r="F11" s="4">
+        <v>3557</v>
+      </c>
+      <c r="G11" s="5">
         <v>3692</v>
       </c>
-      <c r="E11" s="5">
+      <c r="H11" s="5">
         <v>3835</v>
       </c>
-      <c r="F11" s="5">
+      <c r="I11" s="5">
         <v>4010</v>
       </c>
-      <c r="G11" s="6">
+      <c r="J11" s="6">
         <v>4523</v>
       </c>
-      <c r="H11" s="6">
+      <c r="K11" s="6">
         <v>4746</v>
       </c>
-      <c r="I11" s="6">
+      <c r="L11" s="6">
         <v>4973</v>
       </c>
-      <c r="J11" s="6">
+      <c r="M11" s="6">
         <v>4070</v>
       </c>
-      <c r="K11" s="6">
+      <c r="N11" s="6">
         <v>4214</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
@@ -913,32 +1012,41 @@
       <c r="C12" s="4">
         <v>2743</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
+        <v>2882</v>
+      </c>
+      <c r="E12" s="4">
+        <v>2940</v>
+      </c>
+      <c r="F12" s="4">
+        <v>2988</v>
+      </c>
+      <c r="G12" s="5">
         <v>3025</v>
       </c>
-      <c r="E12" s="5">
+      <c r="H12" s="5">
         <v>3050</v>
       </c>
-      <c r="F12" s="5">
+      <c r="I12" s="5">
         <v>3094</v>
       </c>
-      <c r="G12" s="6">
+      <c r="J12" s="6">
         <v>3533</v>
       </c>
-      <c r="H12" s="6">
+      <c r="K12" s="6">
         <v>3621</v>
       </c>
-      <c r="I12" s="6">
+      <c r="L12" s="6">
         <v>3735</v>
       </c>
-      <c r="J12" s="6">
+      <c r="M12" s="6">
         <v>3282</v>
       </c>
-      <c r="K12" s="6">
+      <c r="N12" s="6">
         <v>3311</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>10</v>
       </c>
@@ -948,32 +1056,41 @@
       <c r="C13" s="4">
         <v>2460</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="4">
+        <v>2308</v>
+      </c>
+      <c r="E13" s="4">
+        <v>2348</v>
+      </c>
+      <c r="F13" s="4">
+        <v>2401</v>
+      </c>
+      <c r="G13" s="5">
         <v>2463</v>
       </c>
-      <c r="E13" s="5">
+      <c r="H13" s="5">
         <v>2523</v>
       </c>
-      <c r="F13" s="5">
+      <c r="I13" s="5">
         <v>2585</v>
       </c>
-      <c r="G13" s="6">
+      <c r="J13" s="6">
         <v>2979</v>
       </c>
-      <c r="H13" s="6">
+      <c r="K13" s="6">
         <v>3040</v>
       </c>
-      <c r="I13" s="6">
+      <c r="L13" s="6">
         <v>3087</v>
       </c>
-      <c r="J13" s="6">
+      <c r="M13" s="6">
         <v>2882</v>
       </c>
-      <c r="K13" s="6">
+      <c r="N13" s="6">
         <v>2900</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>11</v>
       </c>
@@ -983,32 +1100,41 @@
       <c r="C14" s="4">
         <v>1872</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
+        <v>1996</v>
+      </c>
+      <c r="E14" s="4">
+        <v>1990</v>
+      </c>
+      <c r="F14" s="4">
+        <v>1983</v>
+      </c>
+      <c r="G14" s="5">
         <v>1977</v>
       </c>
-      <c r="E14" s="5">
+      <c r="H14" s="5">
         <v>1981</v>
       </c>
-      <c r="F14" s="5">
+      <c r="I14" s="5">
         <v>2006</v>
       </c>
-      <c r="G14" s="6">
+      <c r="J14" s="6">
         <v>2348</v>
       </c>
-      <c r="H14" s="6">
+      <c r="K14" s="6">
         <v>2397</v>
       </c>
-      <c r="I14" s="6">
+      <c r="L14" s="6">
         <v>2451</v>
       </c>
-      <c r="J14" s="6">
+      <c r="M14" s="6">
         <v>2307</v>
       </c>
-      <c r="K14" s="6">
+      <c r="N14" s="6">
         <v>2331</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>12</v>
       </c>
@@ -1018,32 +1144,41 @@
       <c r="C15" s="4">
         <v>1343</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="4">
+        <v>1531</v>
+      </c>
+      <c r="E15" s="4">
+        <v>1578</v>
+      </c>
+      <c r="F15" s="4">
+        <v>1618</v>
+      </c>
+      <c r="G15" s="5">
         <v>1647</v>
       </c>
-      <c r="E15" s="5">
+      <c r="H15" s="5">
         <v>1669</v>
       </c>
-      <c r="F15" s="5">
+      <c r="I15" s="5">
         <v>1681</v>
       </c>
-      <c r="G15" s="6">
+      <c r="J15" s="6">
         <v>1980</v>
       </c>
-      <c r="H15" s="6">
+      <c r="K15" s="6">
         <v>1980</v>
       </c>
-      <c r="I15" s="6">
+      <c r="L15" s="6">
         <v>1975</v>
       </c>
-      <c r="J15" s="6">
+      <c r="M15" s="6">
         <v>1705</v>
       </c>
-      <c r="K15" s="6">
+      <c r="N15" s="6">
         <v>1752</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>13</v>
       </c>
@@ -1053,32 +1188,41 @@
       <c r="C16" s="9">
         <v>950</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="9">
+        <v>972</v>
+      </c>
+      <c r="E16" s="9">
+        <v>1007</v>
+      </c>
+      <c r="F16" s="9">
+        <v>1054</v>
+      </c>
+      <c r="G16" s="5">
         <v>1106</v>
       </c>
-      <c r="E16" s="5">
+      <c r="H16" s="5">
         <v>1164</v>
       </c>
-      <c r="F16" s="5">
+      <c r="I16" s="5">
         <v>1226</v>
       </c>
-      <c r="G16" s="6">
+      <c r="J16" s="6">
         <v>1457</v>
       </c>
-      <c r="H16" s="6">
+      <c r="K16" s="6">
         <v>1506</v>
       </c>
-      <c r="I16" s="6">
+      <c r="L16" s="6">
         <v>1544</v>
       </c>
-      <c r="J16" s="6">
+      <c r="M16" s="6">
         <v>1203</v>
       </c>
-      <c r="K16" s="6">
+      <c r="N16" s="6">
         <v>1215</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>14</v>
       </c>
@@ -1088,32 +1232,41 @@
       <c r="C17" s="9">
         <v>611</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="9">
+        <v>602</v>
+      </c>
+      <c r="E17" s="9">
+        <v>618</v>
+      </c>
+      <c r="F17" s="9">
+        <v>637</v>
+      </c>
+      <c r="G17" s="5">
         <v>655</v>
       </c>
-      <c r="E17" s="5">
+      <c r="H17" s="5">
         <v>677</v>
       </c>
-      <c r="F17" s="5">
+      <c r="I17" s="5">
         <v>710</v>
       </c>
-      <c r="G17" s="6">
+      <c r="J17" s="6">
         <v>872</v>
       </c>
-      <c r="H17" s="6">
+      <c r="K17" s="6">
         <v>904</v>
       </c>
-      <c r="I17" s="6">
+      <c r="L17" s="6">
         <v>942</v>
       </c>
-      <c r="J17" s="6">
+      <c r="M17" s="6">
         <v>767</v>
       </c>
-      <c r="K17" s="6">
+      <c r="N17" s="6">
         <v>802</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>15</v>
       </c>
@@ -1123,32 +1276,41 @@
       <c r="C18" s="9">
         <v>400</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="9">
+        <v>311</v>
+      </c>
+      <c r="E18" s="9">
+        <v>324</v>
+      </c>
+      <c r="F18" s="9">
+        <v>340</v>
+      </c>
+      <c r="G18" s="5">
         <v>356</v>
       </c>
-      <c r="E18" s="5">
+      <c r="H18" s="5">
         <v>371</v>
       </c>
-      <c r="F18" s="5">
+      <c r="I18" s="5">
         <v>391</v>
       </c>
-      <c r="G18" s="6">
+      <c r="J18" s="6">
         <v>490</v>
       </c>
-      <c r="H18" s="6">
+      <c r="K18" s="6">
         <v>508</v>
       </c>
-      <c r="I18" s="6">
+      <c r="L18" s="6">
         <v>524</v>
       </c>
-      <c r="J18" s="6">
+      <c r="M18" s="6">
         <v>385</v>
       </c>
-      <c r="K18" s="6">
+      <c r="N18" s="6">
         <v>410</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>16</v>
       </c>
@@ -1158,32 +1320,41 @@
       <c r="C19" s="9">
         <v>237</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="9">
+        <v>145</v>
+      </c>
+      <c r="E19" s="9">
+        <v>146</v>
+      </c>
+      <c r="F19" s="9">
+        <v>150</v>
+      </c>
+      <c r="G19" s="5">
         <v>155</v>
       </c>
-      <c r="E19" s="5">
+      <c r="H19" s="5">
         <v>156</v>
       </c>
-      <c r="F19" s="5">
+      <c r="I19" s="5">
         <v>165</v>
       </c>
-      <c r="G19" s="6">
+      <c r="J19" s="6">
         <v>207</v>
       </c>
-      <c r="H19" s="6">
+      <c r="K19" s="6">
         <v>220</v>
       </c>
-      <c r="I19" s="6">
+      <c r="L19" s="6">
         <v>234</v>
       </c>
-      <c r="J19" s="6">
+      <c r="M19" s="6">
         <v>209</v>
       </c>
-      <c r="K19" s="6">
+      <c r="N19" s="6">
         <v>195</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>17</v>
       </c>
@@ -1193,46 +1364,58 @@
       <c r="C20" s="9">
         <v>211</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="9">
+        <v>141</v>
+      </c>
+      <c r="E20" s="9">
+        <v>133</v>
+      </c>
+      <c r="F20" s="9">
+        <v>127</v>
+      </c>
+      <c r="G20" s="5">
         <v>114</v>
       </c>
-      <c r="E20" s="5">
+      <c r="H20" s="5">
         <v>108</v>
       </c>
-      <c r="F20" s="5">
+      <c r="I20" s="5">
         <v>105</v>
-      </c>
-      <c r="G20" s="6">
-        <v>126</v>
-      </c>
-      <c r="H20" s="6">
-        <v>123</v>
-      </c>
-      <c r="I20" s="6">
-        <v>121</v>
       </c>
       <c r="J20" s="6">
         <v>126</v>
       </c>
       <c r="K20" s="6">
+        <v>123</v>
+      </c>
+      <c r="L20" s="6">
+        <v>121</v>
+      </c>
+      <c r="M20" s="6">
+        <v>126</v>
+      </c>
+      <c r="N20" s="6">
         <v>135</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
       <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B22">
-        <f t="shared" ref="B22:K22" si="0">SUM(B3:B20)-B2</f>
+        <f t="shared" ref="B22:N22" si="0">SUM(B3:B20)-B2</f>
         <v>0</v>
       </c>
       <c r="C22">
@@ -1241,7 +1424,7 @@
       </c>
       <c r="D22">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22">
         <f t="shared" si="0"/>
@@ -1249,30 +1432,42 @@
       </c>
       <c r="F22">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="H22">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J22">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="K22">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1280,8 +1475,11 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1289,8 +1487,11 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1298,8 +1499,11 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1307,8 +1511,11 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1316,8 +1523,11 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1325,8 +1535,11 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1334,8 +1547,11 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1343,8 +1559,11 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1352,8 +1571,11 @@
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1361,8 +1583,11 @@
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1370,8 +1595,11 @@
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1379,8 +1607,11 @@
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1388,8 +1619,11 @@
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1397,8 +1631,11 @@
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1406,6 +1643,9 @@
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1415,15 +1655,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E06D79D5-469C-47C0-8135-942554D5F207}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="11.42578125" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" customWidth="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="1" max="8" width="11.42578125" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -1434,31 +1674,40 @@
         <v>1927</v>
       </c>
       <c r="D1" s="7">
+        <v>1934</v>
+      </c>
+      <c r="E1" s="7">
+        <v>1935</v>
+      </c>
+      <c r="F1" s="7">
+        <v>1936</v>
+      </c>
+      <c r="G1" s="7">
         <v>1937</v>
       </c>
-      <c r="E1" s="7">
+      <c r="H1" s="7">
         <v>1938</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="7">
+      <c r="K1" s="7">
         <v>1940</v>
       </c>
-      <c r="I1" s="7">
+      <c r="L1" s="7">
         <v>1941</v>
       </c>
-      <c r="J1" s="7">
+      <c r="M1" s="7">
         <v>1946</v>
       </c>
-      <c r="K1" s="7">
+      <c r="N1" s="7">
         <v>1947</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
@@ -1468,32 +1717,41 @@
       <c r="C2" s="4">
         <v>76832</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="4">
+        <v>81544</v>
+      </c>
+      <c r="E2" s="4">
+        <v>82280</v>
+      </c>
+      <c r="F2" s="4">
+        <v>83309</v>
+      </c>
+      <c r="G2" s="5">
         <v>84577</v>
       </c>
-      <c r="E2" s="5">
+      <c r="H2" s="5">
         <v>86226</v>
       </c>
-      <c r="F2" s="4">
+      <c r="I2" s="4">
         <v>87850</v>
       </c>
-      <c r="G2" s="4">
+      <c r="J2" s="4">
         <v>98340</v>
       </c>
-      <c r="H2">
+      <c r="K2">
         <v>100283</v>
       </c>
-      <c r="I2" s="6">
+      <c r="L2" s="6">
         <v>101705</v>
       </c>
-      <c r="J2" s="6">
+      <c r="M2" s="6">
         <v>96184</v>
       </c>
-      <c r="K2" s="6">
+      <c r="N2" s="6">
         <v>96869</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1503,32 +1761,41 @@
       <c r="C3" s="4">
         <v>11751</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="4">
+        <v>10205</v>
+      </c>
+      <c r="E3" s="4">
+        <v>9576</v>
+      </c>
+      <c r="F3" s="4">
+        <v>9313</v>
+      </c>
+      <c r="G3" s="5">
         <v>9360</v>
       </c>
-      <c r="E3" s="5">
+      <c r="H3" s="5">
         <v>9952</v>
       </c>
-      <c r="F3" s="5">
+      <c r="I3" s="5">
         <v>10574</v>
       </c>
-      <c r="G3" s="5">
+      <c r="J3" s="5">
         <v>11550</v>
       </c>
-      <c r="H3">
+      <c r="K3">
         <v>12633</v>
       </c>
-      <c r="I3" s="6">
+      <c r="L3" s="6">
         <v>13092</v>
       </c>
-      <c r="J3" s="6">
+      <c r="M3" s="6">
         <v>6632</v>
       </c>
-      <c r="K3" s="6">
+      <c r="N3" s="6">
         <v>6500</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1538,32 +1805,41 @@
       <c r="C4" s="4">
         <v>7754</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
+        <v>10706</v>
+      </c>
+      <c r="E4" s="4">
+        <v>10728</v>
+      </c>
+      <c r="F4" s="4">
+        <v>10557</v>
+      </c>
+      <c r="G4" s="5">
         <v>10212</v>
       </c>
-      <c r="E4" s="5">
+      <c r="H4" s="5">
         <v>9703</v>
       </c>
-      <c r="F4" s="5">
+      <c r="I4" s="5">
         <v>9142</v>
       </c>
-      <c r="G4" s="5">
+      <c r="J4" s="5">
         <v>10118</v>
       </c>
-      <c r="H4">
+      <c r="K4">
         <v>9517</v>
       </c>
-      <c r="I4" s="6">
+      <c r="L4" s="6">
         <v>9212</v>
       </c>
-      <c r="J4" s="6">
+      <c r="M4" s="6">
         <v>11054</v>
       </c>
-      <c r="K4" s="6">
+      <c r="N4" s="6">
         <v>10909</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1573,32 +1849,41 @@
       <c r="C5" s="4">
         <v>8877</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
+        <v>7962</v>
+      </c>
+      <c r="E5" s="4">
+        <v>8552</v>
+      </c>
+      <c r="F5" s="4">
+        <v>9204</v>
+      </c>
+      <c r="G5" s="5">
         <v>9812</v>
       </c>
-      <c r="E5" s="5">
+      <c r="H5" s="5">
         <v>10267</v>
       </c>
-      <c r="F5" s="5">
+      <c r="I5" s="5">
         <v>10513</v>
       </c>
-      <c r="G5" s="5">
+      <c r="J5" s="5">
         <v>11624</v>
       </c>
-      <c r="H5">
+      <c r="K5">
         <v>11625</v>
       </c>
-      <c r="I5" s="6">
+      <c r="L5" s="6">
         <v>11416</v>
       </c>
-      <c r="J5" s="6">
+      <c r="M5" s="6">
         <v>8900</v>
       </c>
-      <c r="K5" s="6">
+      <c r="N5" s="6">
         <v>8907</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
@@ -1608,32 +1893,41 @@
       <c r="C6" s="4">
         <v>8716</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
+        <v>7526</v>
+      </c>
+      <c r="E6" s="4">
+        <v>7194</v>
+      </c>
+      <c r="F6" s="4">
+        <v>7033</v>
+      </c>
+      <c r="G6" s="5">
         <v>7093</v>
       </c>
-      <c r="E6" s="5">
+      <c r="H6" s="5">
         <v>7369</v>
       </c>
-      <c r="F6" s="5">
+      <c r="I6" s="5">
         <v>7829</v>
       </c>
-      <c r="G6" s="5">
+      <c r="J6" s="5">
         <v>8823</v>
       </c>
-      <c r="H6">
+      <c r="K6">
         <v>9474</v>
       </c>
-      <c r="I6" s="6">
+      <c r="L6" s="6">
         <v>10158</v>
       </c>
-      <c r="J6" s="6">
+      <c r="M6" s="6">
         <v>10880</v>
       </c>
-      <c r="K6" s="6">
+      <c r="N6" s="6">
         <v>10598</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
@@ -1643,32 +1937,41 @@
       <c r="C7" s="4">
         <v>7258</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
+        <v>8642</v>
+      </c>
+      <c r="E7" s="4">
+        <v>8695</v>
+      </c>
+      <c r="F7" s="4">
+        <v>8547</v>
+      </c>
+      <c r="G7" s="5">
         <v>8215</v>
       </c>
-      <c r="E7" s="5">
+      <c r="H7" s="5">
         <v>7786</v>
       </c>
-      <c r="F7" s="5">
+      <c r="I7" s="5">
         <v>7367</v>
       </c>
-      <c r="G7" s="5">
+      <c r="J7" s="5">
         <v>8177</v>
       </c>
-      <c r="H7">
+      <c r="K7">
         <v>7821</v>
       </c>
-      <c r="I7" s="6">
+      <c r="L7" s="6">
         <v>7669</v>
       </c>
-      <c r="J7" s="6">
+      <c r="M7" s="6">
         <v>9023</v>
       </c>
-      <c r="K7" s="6">
+      <c r="N7" s="6">
         <v>9600</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
@@ -1678,32 +1981,41 @@
       <c r="C8" s="4">
         <v>6383</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
+        <v>7091</v>
+      </c>
+      <c r="E8" s="4">
+        <v>7343</v>
+      </c>
+      <c r="F8" s="4">
+        <v>7626</v>
+      </c>
+      <c r="G8" s="5">
         <v>7925</v>
       </c>
-      <c r="E8" s="5">
+      <c r="H8" s="5">
         <v>8210</v>
       </c>
-      <c r="F8" s="5">
+      <c r="I8" s="5">
         <v>8426</v>
       </c>
-      <c r="G8" s="5">
+      <c r="J8" s="5">
         <v>9400</v>
       </c>
-      <c r="H8">
+      <c r="K8">
         <v>9459</v>
       </c>
-      <c r="I8" s="6">
+      <c r="L8" s="6">
         <v>9286</v>
       </c>
-      <c r="J8" s="6">
+      <c r="M8" s="6">
         <v>6648</v>
       </c>
-      <c r="K8" s="6">
+      <c r="N8" s="6">
         <v>6781</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>6</v>
       </c>
@@ -1713,32 +2025,41 @@
       <c r="C9" s="4">
         <v>4737</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="4">
+        <v>6165</v>
+      </c>
+      <c r="E9" s="4">
+        <v>6253</v>
+      </c>
+      <c r="F9" s="4">
+        <v>6342</v>
+      </c>
+      <c r="G9" s="5">
         <v>6469</v>
       </c>
-      <c r="E9" s="5">
+      <c r="H9" s="5">
         <v>6652</v>
       </c>
-      <c r="F9" s="5">
+      <c r="I9" s="5">
         <v>6881</v>
       </c>
-      <c r="G9" s="5">
+      <c r="J9" s="5">
         <v>7740</v>
       </c>
-      <c r="H9">
+      <c r="K9">
         <v>8011</v>
       </c>
-      <c r="I9" s="6">
+      <c r="L9" s="6">
         <v>8303</v>
       </c>
-      <c r="J9" s="6">
+      <c r="M9" s="6">
         <v>7996</v>
       </c>
-      <c r="K9" s="6">
+      <c r="N9" s="6">
         <v>7590</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
@@ -1748,32 +2069,41 @@
       <c r="C10" s="4">
         <v>4131</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
+        <v>4777</v>
+      </c>
+      <c r="E10" s="4">
+        <v>5075</v>
+      </c>
+      <c r="F10" s="4">
+        <v>5370</v>
+      </c>
+      <c r="G10" s="5">
         <v>5625</v>
       </c>
-      <c r="E10" s="5">
+      <c r="H10" s="5">
         <v>5820</v>
       </c>
-      <c r="F10" s="5">
+      <c r="I10" s="5">
         <v>5960</v>
       </c>
-      <c r="G10" s="5">
+      <c r="J10" s="5">
         <v>6699</v>
       </c>
-      <c r="H10">
+      <c r="K10">
         <v>6818</v>
       </c>
-      <c r="I10" s="6">
+      <c r="L10" s="6">
         <v>6928</v>
       </c>
-      <c r="J10" s="6">
+      <c r="M10" s="6">
         <v>7528</v>
       </c>
-      <c r="K10" s="6">
+      <c r="N10" s="6">
         <v>7697</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
@@ -1783,32 +2113,41 @@
       <c r="C11" s="4">
         <v>3644</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="4">
+        <v>3807</v>
+      </c>
+      <c r="E11" s="4">
+        <v>3862</v>
+      </c>
+      <c r="F11" s="4">
+        <v>3964</v>
+      </c>
+      <c r="G11" s="5">
         <v>4121</v>
       </c>
-      <c r="E11" s="5">
+      <c r="H11" s="5">
         <v>4335</v>
       </c>
-      <c r="F11" s="5">
+      <c r="I11" s="5">
         <v>4603</v>
       </c>
-      <c r="G11" s="5">
+      <c r="J11" s="5">
         <v>5210</v>
       </c>
-      <c r="H11">
+      <c r="K11">
         <v>5522</v>
       </c>
-      <c r="I11" s="6">
+      <c r="L11" s="6">
         <v>5827</v>
       </c>
-      <c r="J11" s="6">
+      <c r="M11" s="6">
         <v>6509</v>
       </c>
-      <c r="K11" s="6">
+      <c r="N11" s="6">
         <v>6597</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
@@ -1818,32 +2157,41 @@
       <c r="C12" s="4">
         <v>3400</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
+        <v>3408</v>
+      </c>
+      <c r="E12" s="4">
+        <v>3473</v>
+      </c>
+      <c r="F12" s="4">
+        <v>3529</v>
+      </c>
+      <c r="G12" s="5">
         <v>3575</v>
       </c>
-      <c r="E12" s="5">
+      <c r="H12" s="5">
         <v>3612</v>
       </c>
-      <c r="F12" s="5">
+      <c r="I12" s="5">
         <v>3651</v>
       </c>
-      <c r="G12" s="5">
+      <c r="J12" s="5">
         <v>4176</v>
       </c>
-      <c r="H12">
+      <c r="K12">
         <v>4246</v>
       </c>
-      <c r="I12" s="6">
+      <c r="L12" s="6">
         <v>4357</v>
       </c>
-      <c r="J12" s="6">
+      <c r="M12" s="6">
         <v>5418</v>
       </c>
-      <c r="K12" s="6">
+      <c r="N12" s="6">
         <v>5662</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>10</v>
       </c>
@@ -1853,32 +2201,41 @@
       <c r="C13" s="4">
         <v>2933</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="4">
+        <v>3101</v>
+      </c>
+      <c r="E13" s="4">
+        <v>3113</v>
+      </c>
+      <c r="F13" s="4">
+        <v>3123</v>
+      </c>
+      <c r="G13" s="5">
         <v>3140</v>
       </c>
-      <c r="E13" s="5">
+      <c r="H13" s="5">
         <v>3180</v>
       </c>
-      <c r="F13" s="5">
+      <c r="I13" s="5">
         <v>3247</v>
       </c>
-      <c r="G13" s="5">
+      <c r="J13" s="5">
         <v>3718</v>
       </c>
-      <c r="H13">
+      <c r="K13">
         <v>3790</v>
       </c>
-      <c r="I13" s="6">
+      <c r="L13" s="6">
         <v>3848</v>
       </c>
-      <c r="J13" s="6">
+      <c r="M13" s="6">
         <v>3967</v>
       </c>
-      <c r="K13" s="6">
+      <c r="N13" s="6">
         <v>4116</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>11</v>
       </c>
@@ -1888,32 +2245,41 @@
       <c r="C14" s="4">
         <v>2361</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
+        <v>2699</v>
+      </c>
+      <c r="E14" s="4">
+        <v>2755</v>
+      </c>
+      <c r="F14" s="4">
+        <v>2806</v>
+      </c>
+      <c r="G14" s="5">
         <v>2854</v>
       </c>
-      <c r="E14" s="5">
+      <c r="H14" s="5">
         <v>2891</v>
       </c>
-      <c r="F14" s="5">
+      <c r="I14" s="5">
         <v>2919</v>
       </c>
-      <c r="G14" s="5">
+      <c r="J14" s="5">
         <v>3333</v>
       </c>
-      <c r="H14">
+      <c r="K14">
         <v>3352</v>
       </c>
-      <c r="I14" s="6">
+      <c r="L14" s="6">
         <v>3362</v>
       </c>
-      <c r="J14" s="6">
+      <c r="M14" s="6">
         <v>3407</v>
       </c>
-      <c r="K14" s="6">
+      <c r="N14" s="6">
         <v>3453</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>12</v>
       </c>
@@ -1923,32 +2289,41 @@
       <c r="C15" s="4">
         <v>1684</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="4">
+        <v>2125</v>
+      </c>
+      <c r="E15" s="4">
+        <v>2190</v>
+      </c>
+      <c r="F15" s="4">
+        <v>2258</v>
+      </c>
+      <c r="G15" s="5">
         <v>2331</v>
       </c>
-      <c r="E15" s="5">
+      <c r="H15" s="5">
         <v>2405</v>
       </c>
-      <c r="F15" s="5">
+      <c r="I15" s="5">
         <v>2477</v>
       </c>
-      <c r="G15" s="5">
+      <c r="J15" s="5">
         <v>2825</v>
       </c>
-      <c r="H15">
+      <c r="K15">
         <v>2882</v>
       </c>
-      <c r="I15" s="6">
+      <c r="L15" s="6">
         <v>2930</v>
       </c>
-      <c r="J15" s="6">
+      <c r="M15" s="6">
         <v>2848</v>
       </c>
-      <c r="K15" s="6">
+      <c r="N15" s="6">
         <v>2875</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>13</v>
       </c>
@@ -1958,32 +2333,41 @@
       <c r="C16" s="4">
         <v>1229</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="4">
+        <v>1447</v>
+      </c>
+      <c r="E16" s="4">
+        <v>1532</v>
+      </c>
+      <c r="F16" s="4">
+        <v>1620</v>
+      </c>
+      <c r="G16" s="5">
         <v>1713</v>
       </c>
-      <c r="E16" s="5">
+      <c r="H16" s="5">
         <v>1796</v>
       </c>
-      <c r="F16" s="5">
+      <c r="I16" s="5">
         <v>1870</v>
       </c>
-      <c r="G16" s="5">
+      <c r="J16" s="5">
         <v>2145</v>
       </c>
-      <c r="H16">
+      <c r="K16">
         <v>2208</v>
       </c>
-      <c r="I16" s="6">
+      <c r="L16" s="6">
         <v>2266</v>
       </c>
-      <c r="J16" s="6">
+      <c r="M16" s="6">
         <v>2283</v>
       </c>
-      <c r="K16" s="6">
+      <c r="N16" s="6">
         <v>2340</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>14</v>
       </c>
@@ -1993,32 +2377,41 @@
       <c r="C17" s="9">
         <v>830</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="9">
+        <v>893</v>
+      </c>
+      <c r="E17" s="9">
+        <v>930</v>
+      </c>
+      <c r="F17" s="9">
+        <v>978</v>
+      </c>
+      <c r="G17" s="5">
         <v>1041</v>
       </c>
-      <c r="E17" s="5">
+      <c r="H17" s="5">
         <v>1109</v>
       </c>
-      <c r="F17" s="5">
+      <c r="I17" s="5">
         <v>1188</v>
       </c>
-      <c r="G17" s="5">
+      <c r="J17" s="5">
         <v>1383</v>
       </c>
-      <c r="H17">
+      <c r="K17">
         <v>1453</v>
       </c>
-      <c r="I17" s="6">
+      <c r="L17" s="6">
         <v>1522</v>
       </c>
-      <c r="J17" s="6">
+      <c r="M17" s="6">
         <v>1563</v>
       </c>
-      <c r="K17" s="6">
+      <c r="N17" s="6">
         <v>1626</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>15</v>
       </c>
@@ -2028,32 +2421,41 @@
       <c r="C18" s="9">
         <v>564</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="9">
+        <v>510</v>
+      </c>
+      <c r="E18" s="9">
+        <v>538</v>
+      </c>
+      <c r="F18" s="9">
+        <v>567</v>
+      </c>
+      <c r="G18" s="5">
         <v>600</v>
       </c>
-      <c r="E18" s="5">
+      <c r="H18" s="5">
         <v>627</v>
       </c>
-      <c r="F18" s="5">
+      <c r="I18" s="5">
         <v>657</v>
       </c>
-      <c r="G18" s="5">
+      <c r="J18" s="5">
         <v>786</v>
       </c>
-      <c r="H18">
+      <c r="K18">
         <v>819</v>
       </c>
-      <c r="I18" s="6">
+      <c r="L18" s="6">
         <v>853</v>
       </c>
-      <c r="J18" s="6">
+      <c r="M18" s="6">
         <v>865</v>
       </c>
-      <c r="K18" s="6">
+      <c r="N18" s="6">
         <v>930</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>16</v>
       </c>
@@ -2063,32 +2465,41 @@
       <c r="C19" s="9">
         <v>324</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="9">
+        <v>244</v>
+      </c>
+      <c r="E19" s="9">
+        <v>247</v>
+      </c>
+      <c r="F19" s="9">
+        <v>257</v>
+      </c>
+      <c r="G19" s="5">
         <v>277</v>
       </c>
-      <c r="E19" s="5">
+      <c r="H19" s="5">
         <v>299</v>
       </c>
-      <c r="F19" s="5">
+      <c r="I19" s="5">
         <v>327</v>
       </c>
-      <c r="G19" s="5">
+      <c r="J19" s="5">
         <v>383</v>
       </c>
-      <c r="H19">
+      <c r="K19">
         <v>406</v>
       </c>
-      <c r="I19" s="6">
+      <c r="L19" s="6">
         <v>430</v>
       </c>
-      <c r="J19" s="6">
+      <c r="M19" s="6">
         <v>405</v>
       </c>
-      <c r="K19" s="6">
+      <c r="N19" s="6">
         <v>417</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>17</v>
       </c>
@@ -2098,41 +2509,50 @@
       <c r="C20" s="9">
         <v>258</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="9">
+        <v>236</v>
+      </c>
+      <c r="E20" s="9">
+        <v>225</v>
+      </c>
+      <c r="F20" s="9">
+        <v>217</v>
+      </c>
+      <c r="G20" s="5">
         <v>213</v>
       </c>
-      <c r="E20" s="5">
+      <c r="H20" s="5">
         <v>215</v>
       </c>
-      <c r="F20" s="5">
+      <c r="I20" s="5">
         <v>219</v>
       </c>
-      <c r="G20" s="5">
+      <c r="J20" s="5">
         <v>252</v>
       </c>
-      <c r="H20">
+      <c r="K20">
         <v>247</v>
       </c>
-      <c r="I20" s="6">
+      <c r="L20" s="6">
         <v>247</v>
       </c>
-      <c r="J20" s="6">
+      <c r="M20" s="6">
         <v>258</v>
       </c>
-      <c r="K20" s="6">
+      <c r="N20" s="6">
         <v>270</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B22">
-        <f t="shared" ref="B22:J22" si="0">SUM(B3:B20)-B2</f>
+        <f t="shared" ref="B22:M22" si="0">SUM(B3:B20)-B2</f>
         <v>3</v>
       </c>
       <c r="C22">
@@ -2141,39 +2561,51 @@
       </c>
       <c r="D22">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E22">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G22">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="H22">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22">
         <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K22">
-        <f>SUM(K3:K20)-K2</f>
+      <c r="L22">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <f>SUM(N3:N20)-N2</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D23" s="8"/>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G23" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
